--- a/data/Tuğçe proje ödevi.xlsx
+++ b/data/Tuğçe proje ödevi.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\muhasebe06\Desktop\ÇİĞDEM\ÇETE\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Furkan\Desktop\YipranmaAnatomisi\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D85265F-116E-4B01-A6F1-8B3C5D96D8B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11820"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sayfa1" sheetId="1" r:id="rId1"/>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="836" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="843" uniqueCount="67">
   <si>
     <t>Meslek Nedir</t>
   </si>
@@ -98,48 +99,24 @@
     <t>Kel</t>
   </si>
   <si>
-    <t>Marangoz</t>
-  </si>
-  <si>
     <t>10</t>
   </si>
   <si>
     <t>Var</t>
   </si>
   <si>
-    <t>Oto Kaporta</t>
-  </si>
-  <si>
-    <t>Dokuma İşçisi</t>
-  </si>
-  <si>
     <t>Sigortacı</t>
   </si>
   <si>
-    <t>Kellik Başlangıcı</t>
-  </si>
-  <si>
-    <t>Biraz Kel</t>
-  </si>
-  <si>
-    <t>Ziraat Mühendisi</t>
-  </si>
-  <si>
     <t>4</t>
   </si>
   <si>
-    <t>Süre yok</t>
-  </si>
-  <si>
     <t>Yarı Kel</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
-    <t>Psikolojik Danışman</t>
-  </si>
-  <si>
     <t>9</t>
   </si>
   <si>
@@ -152,30 +129,18 @@
     <t>6</t>
   </si>
   <si>
-    <t>Kayak Anterenörü</t>
-  </si>
-  <si>
     <t>16</t>
   </si>
   <si>
-    <t>Kaykay Sürücüsü</t>
-  </si>
-  <si>
     <t>2</t>
   </si>
   <si>
-    <t>Şair</t>
-  </si>
-  <si>
     <t>12</t>
   </si>
   <si>
     <t>13</t>
   </si>
   <si>
-    <t>Emekli</t>
-  </si>
-  <si>
     <t>7-8</t>
   </si>
   <si>
@@ -197,15 +162,9 @@
     <t>7,5</t>
   </si>
   <si>
-    <t>Psikiyatrist</t>
-  </si>
-  <si>
     <t>Avukat</t>
   </si>
   <si>
-    <t>Kel Sayılır</t>
-  </si>
-  <si>
     <t>Güvenlik</t>
   </si>
   <si>
@@ -218,21 +177,12 @@
     <t>Ensaf</t>
   </si>
   <si>
-    <t>Emekli Öğretmen</t>
-  </si>
-  <si>
-    <t>Satış Danışmanı</t>
-  </si>
-  <si>
     <t>Pazarlama</t>
   </si>
   <si>
     <t>Öğrenci</t>
   </si>
   <si>
-    <t>Temizlik</t>
-  </si>
-  <si>
     <t>9-10</t>
   </si>
   <si>
@@ -245,9 +195,6 @@
     <t>Hemşire</t>
   </si>
   <si>
-    <t>Trafik Polisi</t>
-  </si>
-  <si>
     <t>Çiftçi</t>
   </si>
   <si>
@@ -257,52 +204,37 @@
     <t>İdareci</t>
   </si>
   <si>
-    <t>Acil Tıp Teknisyeni</t>
-  </si>
-  <si>
     <t>Sağlık Personeli</t>
   </si>
   <si>
-    <t>Şöför</t>
-  </si>
-  <si>
-    <t>Tıbbi Sekreter</t>
-  </si>
-  <si>
     <t>Bankacı</t>
   </si>
   <si>
-    <t>Market Müdürü</t>
-  </si>
-  <si>
-    <t>Dişçi</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>Nöbet</t>
-  </si>
-  <si>
-    <t>Müdür</t>
-  </si>
-  <si>
     <t>Temizlik Personeli</t>
   </si>
   <si>
     <t>Ev Hanımı</t>
   </si>
   <si>
-    <t>Mali Müşavir</t>
-  </si>
-  <si>
-    <t>İnsan Kaynakları Müdürü</t>
+    <t>Doktor</t>
+  </si>
+  <si>
+    <t>Tamirci</t>
+  </si>
+  <si>
+    <t>Şoför</t>
+  </si>
+  <si>
+    <t>Sporcu</t>
+  </si>
+  <si>
+    <t>Sanatçı</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -643,23 +575,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L105"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.109375" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="8" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.5546875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="8" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.85546875" customWidth="1"/>
+    <col min="11" max="11" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" s="2" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="B1" s="4" t="s">
         <v>7</v>
       </c>
@@ -694,7 +626,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -732,7 +664,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -770,7 +702,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -808,7 +740,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <v>4</v>
       </c>
@@ -816,19 +748,19 @@
         <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D5">
         <v>51</v>
       </c>
       <c r="E5" t="s">
-        <v>23</v>
+        <v>63</v>
       </c>
       <c r="F5">
         <v>35</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H5">
         <v>4</v>
@@ -837,7 +769,7 @@
         <v>15</v>
       </c>
       <c r="J5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K5" t="s">
         <v>16</v>
@@ -846,7 +778,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <v>5</v>
       </c>
@@ -860,7 +792,7 @@
         <v>52</v>
       </c>
       <c r="E6" t="s">
-        <v>26</v>
+        <v>63</v>
       </c>
       <c r="F6">
         <v>40</v>
@@ -884,7 +816,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <v>6</v>
       </c>
@@ -898,7 +830,7 @@
         <v>52</v>
       </c>
       <c r="E7" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="F7">
         <v>30</v>
@@ -913,7 +845,7 @@
         <v>15</v>
       </c>
       <c r="J7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K7" t="s">
         <v>16</v>
@@ -922,7 +854,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
         <v>7</v>
       </c>
@@ -936,13 +868,13 @@
         <v>47</v>
       </c>
       <c r="E8" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F8">
         <v>20</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="H8">
         <v>4</v>
@@ -960,7 +892,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
         <v>8</v>
       </c>
@@ -968,19 +900,19 @@
         <v>11</v>
       </c>
       <c r="C9" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D9">
         <v>48</v>
       </c>
       <c r="E9" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="F9">
         <v>21</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="H9">
         <v>0</v>
@@ -989,7 +921,7 @@
         <v>15</v>
       </c>
       <c r="J9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K9" t="s">
         <v>15</v>
@@ -998,7 +930,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
         <v>9</v>
       </c>
@@ -1006,7 +938,7 @@
         <v>11</v>
       </c>
       <c r="C10" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="D10">
         <v>59</v>
@@ -1018,7 +950,7 @@
         <v>35</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="H10">
         <v>3</v>
@@ -1036,7 +968,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
         <v>10</v>
       </c>
@@ -1050,13 +982,13 @@
         <v>36</v>
       </c>
       <c r="E11" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="F11">
         <v>13</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="H11">
         <v>3</v>
@@ -1074,7 +1006,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
         <v>11</v>
       </c>
@@ -1103,7 +1035,7 @@
         <v>16</v>
       </c>
       <c r="J12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K12" t="s">
         <v>16</v>
@@ -1112,7 +1044,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="3">
         <v>12</v>
       </c>
@@ -1120,7 +1052,7 @@
         <v>11</v>
       </c>
       <c r="C13" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="D13">
         <v>65</v>
@@ -1132,7 +1064,7 @@
         <v>42</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="H13">
         <v>4</v>
@@ -1141,7 +1073,7 @@
         <v>15</v>
       </c>
       <c r="J13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K13" t="s">
         <v>16</v>
@@ -1150,7 +1082,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
         <v>13</v>
       </c>
@@ -1170,7 +1102,7 @@
         <v>32</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="H14">
         <v>5</v>
@@ -1188,7 +1120,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
         <v>14</v>
       </c>
@@ -1208,7 +1140,7 @@
         <v>35</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="H15">
         <v>2</v>
@@ -1217,7 +1149,7 @@
         <v>15</v>
       </c>
       <c r="J15" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K15" t="s">
         <v>16</v>
@@ -1226,7 +1158,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
         <v>15</v>
       </c>
@@ -1255,7 +1187,7 @@
         <v>15</v>
       </c>
       <c r="J16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K16" t="s">
         <v>16</v>
@@ -1264,7 +1196,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
         <v>16</v>
       </c>
@@ -1293,7 +1225,7 @@
         <v>15</v>
       </c>
       <c r="J17" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K17" t="s">
         <v>15</v>
@@ -1302,7 +1234,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" s="3">
         <v>17</v>
       </c>
@@ -1316,13 +1248,13 @@
         <v>59</v>
       </c>
       <c r="E18" t="s">
-        <v>41</v>
+        <v>65</v>
       </c>
       <c r="F18">
         <v>15</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="H18">
         <v>0</v>
@@ -1340,7 +1272,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
         <v>18</v>
       </c>
@@ -1360,7 +1292,7 @@
         <v>30</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="H19">
         <v>4</v>
@@ -1369,7 +1301,7 @@
         <v>15</v>
       </c>
       <c r="J19" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K19" t="s">
         <v>16</v>
@@ -1378,7 +1310,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" s="3">
         <v>19</v>
       </c>
@@ -1416,7 +1348,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" s="3">
         <v>20</v>
       </c>
@@ -1430,13 +1362,13 @@
         <v>40</v>
       </c>
       <c r="E21" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="F21">
         <v>5</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="H21">
         <v>1</v>
@@ -1454,7 +1386,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" s="3">
         <v>21</v>
       </c>
@@ -1468,13 +1400,13 @@
         <v>59</v>
       </c>
       <c r="E22" t="s">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="F22">
         <v>7</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="H22">
         <v>1</v>
@@ -1492,7 +1424,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" s="3">
         <v>22</v>
       </c>
@@ -1506,10 +1438,13 @@
         <v>65</v>
       </c>
       <c r="E23" t="s">
-        <v>48</v>
+        <v>62</v>
+      </c>
+      <c r="F23">
+        <v>40</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H23">
         <v>3</v>
@@ -1527,7 +1462,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" s="3">
         <v>23</v>
       </c>
@@ -1556,7 +1491,7 @@
         <v>15</v>
       </c>
       <c r="J24" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K24" t="s">
         <v>15</v>
@@ -1565,7 +1500,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" s="3">
         <v>24</v>
       </c>
@@ -1585,7 +1520,7 @@
         <v>29</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="H25">
         <v>3</v>
@@ -1603,15 +1538,15 @@
         <v>16</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" s="3">
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C26" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="D26">
         <v>54</v>
@@ -1623,7 +1558,7 @@
         <v>31</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="H26">
         <v>3</v>
@@ -1641,7 +1576,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" s="3">
         <v>26</v>
       </c>
@@ -1649,7 +1584,7 @@
         <v>11</v>
       </c>
       <c r="C27" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D27">
         <v>58</v>
@@ -1661,7 +1596,7 @@
         <v>35</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="H27">
         <v>2</v>
@@ -1679,7 +1614,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" s="3">
         <v>27</v>
       </c>
@@ -1717,12 +1652,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" s="3">
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C29" t="s">
         <v>12</v>
@@ -1731,13 +1666,13 @@
         <v>47</v>
       </c>
       <c r="E29" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="F29">
         <v>12</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="H29">
         <v>3</v>
@@ -1755,7 +1690,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" s="3">
         <v>29</v>
       </c>
@@ -1769,13 +1704,13 @@
         <v>31</v>
       </c>
       <c r="E30" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="F30">
         <v>7</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="H30">
         <v>3</v>
@@ -1793,7 +1728,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" s="3">
         <v>30</v>
       </c>
@@ -1813,7 +1748,7 @@
         <v>25</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="H31">
         <v>1</v>
@@ -1822,7 +1757,7 @@
         <v>15</v>
       </c>
       <c r="J31" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K31" t="s">
         <v>15</v>
@@ -1831,12 +1766,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" s="3">
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C32" t="s">
         <v>12</v>
@@ -1845,7 +1780,7 @@
         <v>45</v>
       </c>
       <c r="E32" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="F32">
         <v>18</v>
@@ -1869,7 +1804,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" s="3">
         <v>32</v>
       </c>
@@ -1883,13 +1818,13 @@
         <v>49</v>
       </c>
       <c r="E33" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="F33">
         <v>24</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="H33">
         <v>3</v>
@@ -1907,12 +1842,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" s="3">
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C34" t="s">
         <v>12</v>
@@ -1945,12 +1880,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" s="3">
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C35" t="s">
         <v>12</v>
@@ -1974,7 +1909,7 @@
         <v>15</v>
       </c>
       <c r="J35" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K35" t="s">
         <v>16</v>
@@ -1983,7 +1918,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" s="3">
         <v>35</v>
       </c>
@@ -1991,7 +1926,7 @@
         <v>11</v>
       </c>
       <c r="C36" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D36">
         <v>33</v>
@@ -2012,7 +1947,7 @@
         <v>15</v>
       </c>
       <c r="J36" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K36" t="s">
         <v>16</v>
@@ -2021,7 +1956,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" s="3">
         <v>36</v>
       </c>
@@ -2050,7 +1985,7 @@
         <v>15</v>
       </c>
       <c r="J37" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K37" t="s">
         <v>15</v>
@@ -2059,12 +1994,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38" s="3">
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C38" t="s">
         <v>12</v>
@@ -2073,7 +2008,7 @@
         <v>35</v>
       </c>
       <c r="E38" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="F38">
         <v>9</v>
@@ -2088,7 +2023,7 @@
         <v>15</v>
       </c>
       <c r="J38" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K38" t="s">
         <v>16</v>
@@ -2097,15 +2032,15 @@
         <v>16</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" s="3">
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C39" t="s">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="D39">
         <v>55</v>
@@ -2117,7 +2052,7 @@
         <v>35</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H39">
         <v>5</v>
@@ -2135,12 +2070,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" s="3">
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C40" t="s">
         <v>12</v>
@@ -2149,7 +2084,7 @@
         <v>37</v>
       </c>
       <c r="E40" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="F40">
         <v>6</v>
@@ -2164,7 +2099,7 @@
         <v>15</v>
       </c>
       <c r="J40" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K40" t="s">
         <v>16</v>
@@ -2173,7 +2108,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" s="3">
         <v>40</v>
       </c>
@@ -2187,7 +2122,7 @@
         <v>47</v>
       </c>
       <c r="E41" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="F41">
         <v>23</v>
@@ -2202,7 +2137,7 @@
         <v>15</v>
       </c>
       <c r="J41" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K41" t="s">
         <v>16</v>
@@ -2211,21 +2146,21 @@
         <v>16</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42" s="3">
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C42" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="D42">
         <v>46</v>
       </c>
       <c r="E42" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="F42">
         <v>14</v>
@@ -2249,7 +2184,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43" s="3">
         <v>42</v>
       </c>
@@ -2263,7 +2198,7 @@
         <v>43</v>
       </c>
       <c r="E43" t="s">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="F43">
         <v>22</v>
@@ -2287,12 +2222,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A44" s="3">
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C44" t="s">
         <v>12</v>
@@ -2301,13 +2236,13 @@
         <v>20</v>
       </c>
       <c r="E44" t="s">
-        <v>62</v>
+        <v>13</v>
       </c>
       <c r="F44">
         <v>1</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H44">
         <v>3</v>
@@ -2325,27 +2260,27 @@
         <v>15</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A45" s="3">
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C45" t="s">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="D45">
         <v>54</v>
       </c>
       <c r="E45" t="s">
-        <v>62</v>
+        <v>13</v>
       </c>
       <c r="F45">
         <v>12</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="H45">
         <v>5</v>
@@ -2354,7 +2289,7 @@
         <v>15</v>
       </c>
       <c r="J45" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K45" t="s">
         <v>15</v>
@@ -2363,7 +2298,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A46" s="3">
         <v>45</v>
       </c>
@@ -2377,7 +2312,7 @@
         <v>50</v>
       </c>
       <c r="E46" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="F46">
         <v>10</v>
@@ -2392,7 +2327,7 @@
         <v>15</v>
       </c>
       <c r="J46" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K46" t="s">
         <v>16</v>
@@ -2401,27 +2336,27 @@
         <v>16</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A47" s="3">
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C47" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="D47">
         <v>71</v>
       </c>
       <c r="E47" t="s">
-        <v>63</v>
+        <v>20</v>
       </c>
       <c r="F47">
         <v>28</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="H47">
         <v>4</v>
@@ -2430,7 +2365,7 @@
         <v>15</v>
       </c>
       <c r="J47" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K47" t="s">
         <v>16</v>
@@ -2439,21 +2374,21 @@
         <v>16</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48" s="3">
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C48" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="D48">
         <v>34</v>
       </c>
       <c r="E48" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="F48">
         <v>4</v>
@@ -2477,7 +2412,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A49" s="3">
         <v>48</v>
       </c>
@@ -2491,13 +2426,13 @@
         <v>30</v>
       </c>
       <c r="E49" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="F49">
         <v>5</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="H49">
         <v>5</v>
@@ -2515,7 +2450,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A50" s="3">
         <v>49</v>
       </c>
@@ -2529,7 +2464,13 @@
         <v>63</v>
       </c>
       <c r="E50" t="s">
-        <v>48</v>
+        <v>13</v>
+      </c>
+      <c r="F50">
+        <v>30</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="H50">
         <v>3</v>
@@ -2547,27 +2488,27 @@
         <v>15</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A51" s="3">
         <v>50</v>
       </c>
       <c r="B51" t="s">
+        <v>38</v>
+      </c>
+      <c r="C51" t="s">
+        <v>12</v>
+      </c>
+      <c r="D51">
+        <v>17</v>
+      </c>
+      <c r="E51" t="s">
         <v>50</v>
-      </c>
-      <c r="C51" t="s">
-        <v>12</v>
-      </c>
-      <c r="D51">
-        <v>17</v>
-      </c>
-      <c r="E51" t="s">
-        <v>66</v>
       </c>
       <c r="F51">
         <v>3</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H51">
         <v>3</v>
@@ -2576,7 +2517,7 @@
         <v>15</v>
       </c>
       <c r="J51" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K51" t="s">
         <v>16</v>
@@ -2585,7 +2526,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A52" s="3">
         <v>51</v>
       </c>
@@ -2599,13 +2540,13 @@
         <v>31</v>
       </c>
       <c r="E52" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="F52">
         <v>7</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="H52">
         <v>3</v>
@@ -2623,12 +2564,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A53" s="3">
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C53" t="s">
         <v>12</v>
@@ -2637,13 +2578,13 @@
         <v>54</v>
       </c>
       <c r="E53" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="F53">
         <v>15</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="H53">
         <v>3</v>
@@ -2661,7 +2602,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A54" s="3">
         <v>53</v>
       </c>
@@ -2675,13 +2616,13 @@
         <v>25</v>
       </c>
       <c r="E54" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="F54">
         <v>2</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="H54">
         <v>3</v>
@@ -2699,7 +2640,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A55" s="3">
         <v>54</v>
       </c>
@@ -2713,13 +2654,13 @@
         <v>54</v>
       </c>
       <c r="E55" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="F55">
         <v>20</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="H55">
         <v>4</v>
@@ -2737,12 +2678,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A56" s="3">
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C56" t="s">
         <v>12</v>
@@ -2757,7 +2698,7 @@
         <v>10</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="H56">
         <v>3</v>
@@ -2775,7 +2716,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A57" s="3">
         <v>56</v>
       </c>
@@ -2789,13 +2730,13 @@
         <v>51</v>
       </c>
       <c r="E57" t="s">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="F57">
         <v>25</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="H57">
         <v>5</v>
@@ -2813,7 +2754,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A58" s="3">
         <v>57</v>
       </c>
@@ -2827,7 +2768,7 @@
         <v>25</v>
       </c>
       <c r="E58" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="F58">
         <v>1</v>
@@ -2842,7 +2783,7 @@
         <v>15</v>
       </c>
       <c r="J58" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K58" t="s">
         <v>16</v>
@@ -2851,12 +2792,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A59" s="3">
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C59" t="s">
         <v>22</v>
@@ -2865,7 +2806,7 @@
         <v>53</v>
       </c>
       <c r="E59" t="s">
-        <v>71</v>
+        <v>54</v>
       </c>
       <c r="F59">
         <v>25</v>
@@ -2880,7 +2821,7 @@
         <v>15</v>
       </c>
       <c r="J59" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K59" t="s">
         <v>16</v>
@@ -2889,7 +2830,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A60" s="3">
         <v>59</v>
       </c>
@@ -2903,13 +2844,13 @@
         <v>53</v>
       </c>
       <c r="E60" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="F60">
         <v>53</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="H60">
         <v>5</v>
@@ -2918,7 +2859,7 @@
         <v>15</v>
       </c>
       <c r="J60" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K60" t="s">
         <v>15</v>
@@ -2927,7 +2868,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A61" s="3">
         <v>60</v>
       </c>
@@ -2941,7 +2882,7 @@
         <v>48</v>
       </c>
       <c r="E61" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="F61">
         <v>28</v>
@@ -2956,7 +2897,7 @@
         <v>15</v>
       </c>
       <c r="J61" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K61" t="s">
         <v>15</v>
@@ -2965,7 +2906,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A62" s="3">
         <v>61</v>
       </c>
@@ -2979,13 +2920,13 @@
         <v>41</v>
       </c>
       <c r="E62" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="F62">
         <v>18</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H62">
         <v>4</v>
@@ -2994,7 +2935,7 @@
         <v>15</v>
       </c>
       <c r="J62" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K62" t="s">
         <v>16</v>
@@ -3003,7 +2944,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A63" s="3">
         <v>62</v>
       </c>
@@ -3017,11 +2958,14 @@
         <v>52</v>
       </c>
       <c r="E63" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="F63">
         <v>8</v>
       </c>
+      <c r="G63" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="H63">
         <v>1</v>
       </c>
@@ -3029,7 +2973,7 @@
         <v>15</v>
       </c>
       <c r="J63" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K63" t="s">
         <v>16</v>
@@ -3038,7 +2982,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A64" s="3">
         <v>63</v>
       </c>
@@ -3052,7 +2996,7 @@
         <v>50</v>
       </c>
       <c r="E64" t="s">
-        <v>71</v>
+        <v>54</v>
       </c>
       <c r="F64">
         <v>32</v>
@@ -3067,7 +3011,7 @@
         <v>15</v>
       </c>
       <c r="J64" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K64" t="s">
         <v>16</v>
@@ -3076,12 +3020,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A65" s="3">
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C65" t="s">
         <v>22</v>
@@ -3090,7 +3034,10 @@
         <v>27</v>
       </c>
       <c r="E65" t="s">
-        <v>75</v>
+        <v>57</v>
+      </c>
+      <c r="F65">
+        <v>9</v>
       </c>
       <c r="G65" s="1" t="s">
         <v>21</v>
@@ -3098,6 +3045,9 @@
       <c r="H65">
         <v>1</v>
       </c>
+      <c r="I65" t="s">
+        <v>15</v>
+      </c>
       <c r="J65" t="s">
         <v>17</v>
       </c>
@@ -3108,12 +3058,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A66" s="3">
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C66" t="s">
         <v>22</v>
@@ -3122,7 +3072,7 @@
         <v>45</v>
       </c>
       <c r="E66" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="F66">
         <v>26</v>
@@ -3137,7 +3087,7 @@
         <v>15</v>
       </c>
       <c r="J66" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K66" t="s">
         <v>15</v>
@@ -3146,7 +3096,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A67" s="3">
         <v>66</v>
       </c>
@@ -3160,19 +3110,22 @@
         <v>46</v>
       </c>
       <c r="E67" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="F67">
         <v>23</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H67">
         <v>2</v>
       </c>
+      <c r="I67" t="s">
+        <v>16</v>
+      </c>
       <c r="J67" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K67" t="s">
         <v>16</v>
@@ -3181,12 +3134,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A68" s="3">
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C68" t="s">
         <v>12</v>
@@ -3201,11 +3154,14 @@
         <v>20</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="H68">
         <v>3</v>
       </c>
+      <c r="I68" t="s">
+        <v>15</v>
+      </c>
       <c r="J68" t="s">
         <v>17</v>
       </c>
@@ -3216,7 +3172,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A69" s="3">
         <v>68</v>
       </c>
@@ -3230,7 +3186,7 @@
         <v>46</v>
       </c>
       <c r="E69" t="s">
-        <v>71</v>
+        <v>54</v>
       </c>
       <c r="F69">
         <v>22</v>
@@ -3245,7 +3201,7 @@
         <v>16</v>
       </c>
       <c r="J69" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K69" t="s">
         <v>15</v>
@@ -3254,12 +3210,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A70" s="3">
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C70" t="s">
         <v>12</v>
@@ -3268,7 +3224,7 @@
         <v>42</v>
       </c>
       <c r="E70" t="s">
-        <v>77</v>
+        <v>58</v>
       </c>
       <c r="F70">
         <v>5</v>
@@ -3292,7 +3248,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A71" s="3">
         <v>70</v>
       </c>
@@ -3306,13 +3262,13 @@
         <v>45</v>
       </c>
       <c r="E71" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="F71">
         <v>25</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H71">
         <v>2</v>
@@ -3330,12 +3286,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A72" s="3">
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C72" t="s">
         <v>12</v>
@@ -3344,7 +3300,7 @@
         <v>25</v>
       </c>
       <c r="E72" t="s">
-        <v>79</v>
+        <v>58</v>
       </c>
       <c r="F72">
         <v>5</v>
@@ -3368,7 +3324,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A73" s="3">
         <v>72</v>
       </c>
@@ -3397,7 +3353,7 @@
         <v>15</v>
       </c>
       <c r="J73" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K73" t="s">
         <v>15</v>
@@ -3406,7 +3362,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A74" s="3">
         <v>73</v>
       </c>
@@ -3420,13 +3376,13 @@
         <v>60</v>
       </c>
       <c r="E74" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="F74">
         <v>40</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H74">
         <v>3</v>
@@ -3435,7 +3391,7 @@
         <v>16</v>
       </c>
       <c r="J74" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K74" t="s">
         <v>16</v>
@@ -3444,12 +3400,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A75" s="3">
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C75" t="s">
         <v>22</v>
@@ -3458,7 +3414,7 @@
         <v>46</v>
       </c>
       <c r="E75" t="s">
-        <v>71</v>
+        <v>54</v>
       </c>
       <c r="F75">
         <v>26</v>
@@ -3469,8 +3425,11 @@
       <c r="H75">
         <v>5</v>
       </c>
+      <c r="I75" t="s">
+        <v>16</v>
+      </c>
       <c r="J75" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K75" t="s">
         <v>16</v>
@@ -3479,7 +3438,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A76" s="3">
         <v>75</v>
       </c>
@@ -3493,7 +3452,7 @@
         <v>43</v>
       </c>
       <c r="E76" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="F76">
         <v>19</v>
@@ -3517,7 +3476,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A77" s="3">
         <v>76</v>
       </c>
@@ -3531,7 +3490,7 @@
         <v>46</v>
       </c>
       <c r="E77" t="s">
-        <v>71</v>
+        <v>54</v>
       </c>
       <c r="F77">
         <v>24</v>
@@ -3546,7 +3505,7 @@
         <v>15</v>
       </c>
       <c r="J77" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K77" t="s">
         <v>15</v>
@@ -3555,7 +3514,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A78" s="3">
         <v>77</v>
       </c>
@@ -3584,7 +3543,7 @@
         <v>15</v>
       </c>
       <c r="J78" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K78" t="s">
         <v>16</v>
@@ -3593,12 +3552,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A79" s="3">
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C79" t="s">
         <v>22</v>
@@ -3631,7 +3590,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A80" s="3">
         <v>79</v>
       </c>
@@ -3645,7 +3604,7 @@
         <v>32</v>
       </c>
       <c r="E80" t="s">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="F80">
         <v>3</v>
@@ -3660,7 +3619,7 @@
         <v>15</v>
       </c>
       <c r="J80" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K80" t="s">
         <v>16</v>
@@ -3669,7 +3628,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A81" s="3">
         <v>80</v>
       </c>
@@ -3683,13 +3642,13 @@
         <v>49</v>
       </c>
       <c r="E81" t="s">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="F81">
         <v>8</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="H81">
         <v>4</v>
@@ -3707,7 +3666,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A82" s="3">
         <v>81</v>
       </c>
@@ -3721,7 +3680,7 @@
         <v>47</v>
       </c>
       <c r="E82" t="s">
-        <v>81</v>
+        <v>57</v>
       </c>
       <c r="F82">
         <v>20</v>
@@ -3745,12 +3704,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A83" s="3">
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C83" t="s">
         <v>22</v>
@@ -3774,7 +3733,7 @@
         <v>15</v>
       </c>
       <c r="J83" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K83" t="s">
         <v>16</v>
@@ -3783,12 +3742,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A84" s="3">
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C84" t="s">
         <v>12</v>
@@ -3821,12 +3780,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A85" s="3">
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C85" t="s">
         <v>22</v>
@@ -3835,7 +3794,7 @@
         <v>36</v>
       </c>
       <c r="E85" t="s">
-        <v>82</v>
+        <v>62</v>
       </c>
       <c r="F85">
         <v>10</v>
@@ -3859,12 +3818,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A86" s="3">
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C86" t="s">
         <v>12</v>
@@ -3873,13 +3832,13 @@
         <v>49</v>
       </c>
       <c r="E86" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="F86">
         <v>25</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="H86">
         <v>2</v>
@@ -3888,7 +3847,7 @@
         <v>15</v>
       </c>
       <c r="J86" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K86" t="s">
         <v>16</v>
@@ -3897,12 +3856,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A87" s="3">
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C87" t="s">
         <v>22</v>
@@ -3911,13 +3870,13 @@
         <v>43</v>
       </c>
       <c r="E87" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="F87">
         <v>15</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="H87">
         <v>4</v>
@@ -3926,7 +3885,7 @@
         <v>15</v>
       </c>
       <c r="J87" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K87" t="s">
         <v>15</v>
@@ -3935,12 +3894,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A88" s="3">
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C88" t="s">
         <v>12</v>
@@ -3949,13 +3908,13 @@
         <v>45</v>
       </c>
       <c r="E88" t="s">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="F88">
         <v>25</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H88">
         <v>3</v>
@@ -3973,7 +3932,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A89" s="3">
         <v>88</v>
       </c>
@@ -3987,13 +3946,13 @@
         <v>54</v>
       </c>
       <c r="E89" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="F89">
         <v>30</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>84</v>
+        <v>19</v>
       </c>
       <c r="H89">
         <v>1</v>
@@ -4011,7 +3970,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A90" s="3">
         <v>89</v>
       </c>
@@ -4025,13 +3984,13 @@
         <v>51</v>
       </c>
       <c r="E90" t="s">
-        <v>85</v>
+        <v>57</v>
       </c>
       <c r="F90">
         <v>26</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="H90">
         <v>5</v>
@@ -4049,12 +4008,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A91" s="3">
         <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C91" t="s">
         <v>12</v>
@@ -4063,13 +4022,13 @@
         <v>47</v>
       </c>
       <c r="E91" t="s">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="F91">
         <v>28</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="H91">
         <v>3</v>
@@ -4087,12 +4046,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A92" s="3">
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C92" t="s">
         <v>12</v>
@@ -4116,7 +4075,7 @@
         <v>15</v>
       </c>
       <c r="J92" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K92" t="s">
         <v>16</v>
@@ -4125,12 +4084,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A93" s="3">
         <v>92</v>
       </c>
       <c r="B93" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C93" t="s">
         <v>22</v>
@@ -4163,12 +4122,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A94" s="3">
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C94" t="s">
         <v>22</v>
@@ -4201,7 +4160,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A95" s="3">
         <v>94</v>
       </c>
@@ -4221,7 +4180,7 @@
         <v>15</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H95">
         <v>2</v>
@@ -4230,7 +4189,7 @@
         <v>15</v>
       </c>
       <c r="J95" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K95" t="s">
         <v>16</v>
@@ -4239,7 +4198,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A96" s="3">
         <v>95</v>
       </c>
@@ -4268,7 +4227,7 @@
         <v>15</v>
       </c>
       <c r="J96" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K96" t="s">
         <v>15</v>
@@ -4277,7 +4236,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="97" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A97" s="3">
         <v>96</v>
       </c>
@@ -4291,7 +4250,7 @@
         <v>27</v>
       </c>
       <c r="E97" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="F97">
         <v>3</v>
@@ -4315,7 +4274,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A98" s="3">
         <v>97</v>
       </c>
@@ -4344,7 +4303,7 @@
         <v>15</v>
       </c>
       <c r="J98" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K98" t="s">
         <v>16</v>
@@ -4353,12 +4312,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A99" s="3">
         <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C99" t="s">
         <v>22</v>
@@ -4367,7 +4326,7 @@
         <v>42</v>
       </c>
       <c r="E99" t="s">
-        <v>86</v>
+        <v>60</v>
       </c>
       <c r="F99">
         <v>5</v>
@@ -4382,7 +4341,7 @@
         <v>15</v>
       </c>
       <c r="J99" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K99" t="s">
         <v>16</v>
@@ -4391,12 +4350,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A100" s="3">
         <v>99</v>
       </c>
       <c r="B100" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C100" t="s">
         <v>22</v>
@@ -4405,7 +4364,7 @@
         <v>46</v>
       </c>
       <c r="E100" t="s">
-        <v>86</v>
+        <v>60</v>
       </c>
       <c r="F100">
         <v>12</v>
@@ -4420,7 +4379,7 @@
         <v>16</v>
       </c>
       <c r="J100" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K100" t="s">
         <v>15</v>
@@ -4429,12 +4388,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="101" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A101" s="3">
         <v>100</v>
       </c>
       <c r="B101" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C101" t="s">
         <v>22</v>
@@ -4443,16 +4402,22 @@
         <v>67</v>
       </c>
       <c r="E101" t="s">
-        <v>87</v>
+        <v>61</v>
+      </c>
+      <c r="F101">
+        <v>50</v>
       </c>
       <c r="G101" s="1" t="s">
-        <v>83</v>
+        <v>29</v>
       </c>
       <c r="H101">
         <v>1</v>
       </c>
+      <c r="I101" t="s">
+        <v>15</v>
+      </c>
       <c r="J101" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K101" t="s">
         <v>16</v>
@@ -4461,12 +4426,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="102" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A102" s="3">
         <v>101</v>
       </c>
       <c r="B102" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C102" t="s">
         <v>12</v>
@@ -4475,13 +4440,13 @@
         <v>44</v>
       </c>
       <c r="E102" t="s">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="F102">
         <v>26</v>
       </c>
       <c r="G102" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H102">
         <v>5</v>
@@ -4499,12 +4464,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="103" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A103" s="3">
         <v>102</v>
       </c>
       <c r="B103" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C103" t="s">
         <v>12</v>
@@ -4513,13 +4478,13 @@
         <v>47</v>
       </c>
       <c r="E103" t="s">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="F103">
         <v>31</v>
       </c>
       <c r="G103" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H103">
         <v>5</v>
@@ -4537,7 +4502,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="104" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A104" s="3">
         <v>103</v>
       </c>
@@ -4551,13 +4516,13 @@
         <v>49</v>
       </c>
       <c r="E104" t="s">
-        <v>88</v>
+        <v>47</v>
       </c>
       <c r="F104">
         <v>34</v>
       </c>
       <c r="G104" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H104">
         <v>5</v>
@@ -4575,7 +4540,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="105" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A105" s="3">
         <v>104</v>
       </c>
@@ -4589,13 +4554,13 @@
         <v>50</v>
       </c>
       <c r="E105" t="s">
-        <v>89</v>
+        <v>57</v>
       </c>
       <c r="F105">
         <v>26</v>
       </c>
       <c r="G105" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H105">
         <v>4</v>
@@ -4604,7 +4569,7 @@
         <v>15</v>
       </c>
       <c r="J105" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K105" t="s">
         <v>16</v>
@@ -4614,7 +4579,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L1"/>
+  <autoFilter ref="A1:L1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
